--- a/artfynd/A 2574-2026 artfynd.xlsx
+++ b/artfynd/A 2574-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68197880</v>
+        <v>126591604</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>744033.8382721629</v>
+        <v>744160</v>
       </c>
       <c r="R2" t="n">
-        <v>7175061.609989009</v>
+        <v>7174857</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68197885</v>
+        <v>126591571</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,40 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>744018.91150147</v>
+        <v>744475</v>
       </c>
       <c r="R3" t="n">
-        <v>7175075.487585763</v>
+        <v>7174723</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,64 +855,73 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126591605</v>
+        <v>68197885</v>
       </c>
       <c r="B4" t="n">
-        <v>80184</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarthultmyran, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>744004</v>
+        <v>744019</v>
       </c>
       <c r="R4" t="n">
-        <v>7175058</v>
+        <v>7175075</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,70 +962,64 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126591594</v>
+        <v>126591570</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>744342</v>
+        <v>744081</v>
       </c>
       <c r="R5" t="n">
-        <v>7174693</v>
+        <v>7174948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,18 +1054,12 @@
           <t>2025-07-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar, flera träd</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126591585</v>
+        <v>126591589</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>92556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,42 +1093,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5454</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>744412</v>
+        <v>744331</v>
       </c>
       <c r="R6" t="n">
-        <v>7174653</v>
+        <v>7174735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,53 +1183,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126591575</v>
+        <v>68197880</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarthultmyran, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>744313</v>
+        <v>744034</v>
       </c>
       <c r="R7" t="n">
-        <v>7174751</v>
+        <v>7175062</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,17 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,30 +1274,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126591591</v>
+        <v>126591590</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1381,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>744030</v>
+        <v>744042</v>
       </c>
       <c r="R8" t="n">
-        <v>7175064</v>
+        <v>7174988</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1361,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,14 +1392,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126591593</v>
+        <v>126591591</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1481,19 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>744415</v>
+        <v>744030</v>
       </c>
       <c r="R9" t="n">
-        <v>7174604</v>
+        <v>7175064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1467,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt, långa bålar, flera träd</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,7 +1476,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1562,42 +1498,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126591577</v>
+        <v>126591592</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1605,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>744053</v>
+        <v>744476</v>
       </c>
       <c r="R10" t="n">
-        <v>7174888</v>
+        <v>7174709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,6 +1585,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1676,50 +1608,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126591569</v>
+        <v>126591593</v>
       </c>
       <c r="B11" t="n">
-        <v>58424</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103056</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1727,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>744456</v>
+        <v>744415</v>
       </c>
       <c r="R11" t="n">
-        <v>7174718</v>
+        <v>7174604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1686,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
+          <t>Rikligt, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,6 +1695,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1798,45 +1718,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126591604</v>
+        <v>126591594</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>744160</v>
+        <v>744342</v>
       </c>
       <c r="R12" t="n">
-        <v>7174857</v>
+        <v>7174693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,12 +1794,18 @@
           <t>2025-07-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar, flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1899,53 +1828,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126591572</v>
+        <v>126591595</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>744516</v>
+        <v>744154</v>
       </c>
       <c r="R13" t="n">
-        <v>7174708</v>
+        <v>7174866</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,11 +1899,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,14 +1929,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126591592</v>
+        <v>126591596</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2042,19 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>744476</v>
+        <v>744142</v>
       </c>
       <c r="R14" t="n">
-        <v>7174709</v>
+        <v>7174925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långa bålar, rikligt</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,7 +2013,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2123,14 +2035,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126591602</v>
+        <v>126591597</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2152,16 +2064,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>744018</v>
+        <v>744119</v>
       </c>
       <c r="R15" t="n">
-        <v>7175088</v>
+        <v>7174920</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,7 +2113,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långa bålar</t>
+          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,6 +2122,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2229,53 +2145,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126591584</v>
+        <v>126591598</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>744015</v>
+        <v>744081</v>
       </c>
       <c r="R16" t="n">
-        <v>7175028</v>
+        <v>7174948</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,53 +2246,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126591581</v>
+        <v>126591599</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>744010</v>
+        <v>744069</v>
       </c>
       <c r="R17" t="n">
-        <v>7175003</v>
+        <v>7174983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,11 +2317,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,53 +2347,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126591579</v>
+        <v>126591600</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>744008</v>
+        <v>744023</v>
       </c>
       <c r="R18" t="n">
-        <v>7175023</v>
+        <v>7175031</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,11 +2418,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,11 +2451,11 @@
         <v>126591601</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2667,32 +2549,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126591570</v>
+        <v>126591602</v>
       </c>
       <c r="B20" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>744081</v>
+        <v>744018</v>
       </c>
       <c r="R20" t="n">
-        <v>7174948</v>
+        <v>7175088</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,6 +2620,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,32 +2655,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126591571</v>
+        <v>126591605</v>
       </c>
       <c r="B21" t="n">
-        <v>91549</v>
+        <v>80467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2803,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>744475</v>
+        <v>744004</v>
       </c>
       <c r="R21" t="n">
-        <v>7174723</v>
+        <v>7175058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2869,10 +2756,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126591578</v>
+        <v>126591572</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>744081</v>
+        <v>744516</v>
       </c>
       <c r="R22" t="n">
-        <v>7174948</v>
+        <v>7174708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2983,10 +2870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126591576</v>
+        <v>126591573</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,7 +2903,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3026,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>744244</v>
+        <v>744392</v>
       </c>
       <c r="R23" t="n">
-        <v>7174800</v>
+        <v>7174607</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,7 +2953,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126591580</v>
+        <v>126591574</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,7 +3017,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3140,10 +3027,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>744013</v>
+        <v>744358</v>
       </c>
       <c r="R24" t="n">
-        <v>7175001</v>
+        <v>7174698</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,7 +3067,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3211,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126591597</v>
+        <v>126591575</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3222,26 +3109,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3249,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>744119</v>
+        <v>744313</v>
       </c>
       <c r="R25" t="n">
-        <v>7174920</v>
+        <v>7174751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3289,7 +3181,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långa bålar, rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,7 +3190,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3321,10 +3212,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126591573</v>
+        <v>126591576</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,7 +3245,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3364,10 +3255,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>744392</v>
+        <v>744244</v>
       </c>
       <c r="R26" t="n">
-        <v>7174607</v>
+        <v>7174800</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3404,7 +3295,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126591599</v>
+        <v>126591577</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,34 +3337,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>744069</v>
+        <v>744053</v>
       </c>
       <c r="R27" t="n">
-        <v>7174983</v>
+        <v>7174888</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3506,6 +3405,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126591583</v>
+        <v>126591578</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,21 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,7 +3473,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3579,10 +3483,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>744054</v>
+        <v>744081</v>
       </c>
       <c r="R28" t="n">
-        <v>7174882</v>
+        <v>7174948</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3615,6 +3519,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126591590</v>
+        <v>126591579</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,34 +3565,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>744042</v>
+        <v>744008</v>
       </c>
       <c r="R29" t="n">
-        <v>7174988</v>
+        <v>7175023</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,7 +3637,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långa bålar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126591589</v>
+        <v>126591580</v>
       </c>
       <c r="B30" t="n">
-        <v>92191</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,34 +3679,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5454</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>744331</v>
+        <v>744013</v>
       </c>
       <c r="R30" t="n">
-        <v>7174735</v>
+        <v>7175001</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,6 +3747,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,10 +3782,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126591574</v>
+        <v>126591581</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3895,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>744358</v>
+        <v>744010</v>
       </c>
       <c r="R31" t="n">
-        <v>7174698</v>
+        <v>7175003</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,10 +3896,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126591600</v>
+        <v>126591583</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,34 +3907,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>744023</v>
+        <v>744054</v>
       </c>
       <c r="R32" t="n">
-        <v>7175031</v>
+        <v>7174882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,10 +4005,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126591595</v>
+        <v>126591584</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4078,34 +4016,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>744154</v>
+        <v>744015</v>
       </c>
       <c r="R33" t="n">
-        <v>7174866</v>
+        <v>7175028</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4168,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126591596</v>
+        <v>126591585</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,34 +4125,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>744142</v>
+        <v>744412</v>
       </c>
       <c r="R34" t="n">
-        <v>7174925</v>
+        <v>7174653</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,11 +4193,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4274,10 +4223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126591598</v>
+        <v>126591586</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,34 +4234,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>744081</v>
+        <v>744358</v>
       </c>
       <c r="R35" t="n">
-        <v>7174948</v>
+        <v>7174698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4375,40 +4332,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126591586</v>
+        <v>126591569</v>
       </c>
       <c r="B36" t="n">
-        <v>57887</v>
+        <v>58656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>103056</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4418,10 +4383,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>744358</v>
+        <v>744456</v>
       </c>
       <c r="R36" t="n">
-        <v>7174698</v>
+        <v>7174718</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4454,6 +4419,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 2574-2026 artfynd.xlsx
+++ b/artfynd/A 2574-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591604</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591571</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68197885</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591570</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591589</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68197880</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591590</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591591</t>
         </is>
       </c>
     </row>
@@ -1605,6 +1650,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591592</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591594</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591595</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591596</t>
         </is>
       </c>
     </row>
@@ -2142,6 +2212,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591597</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2243,6 +2318,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591598</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591599</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2445,6 +2530,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591600</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2546,6 +2636,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591601</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2652,6 +2747,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591602</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2753,6 +2853,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591605</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2867,6 +2972,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591572</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2981,6 +3091,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591573</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3095,6 +3210,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591574</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591575</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3323,6 +3448,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591576</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3437,6 +3567,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591577</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591578</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3665,6 +3805,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591579</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3779,6 +3924,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591580</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3893,6 +4043,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591581</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4002,6 +4157,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591583</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4111,6 +4271,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591584</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4220,6 +4385,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591585</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4329,6 +4499,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591586</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4451,8 +4626,50 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591569</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>